--- a/out/Сверка цен.xlsx
+++ b/out/Сверка цен.xlsx
@@ -9,22 +9,26 @@
   <sheets>
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Расхождения" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Нет в прайсе" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="В прайсе, но не зелёные" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Кириллица в артикуле" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Зелёные — нет в фидах" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Разбор прайса" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Параметры прогона" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Пропущено — красные строки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Нет в прайсе" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="В прайсе, но не зелёные" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Кириллица в артикуле" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Зелёные — нет в фидах" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Красная разметка фидов" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Разбор прайса" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Параметры прогона" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка'!$A$3:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Расхождения'!$A$3:$K$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Нет в прайсе'!$A$3:$G$447</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'В прайсе, но не зелёные'!$A$3:$H$625</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Кириллица в артикуле'!$A$3:$H$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Зелёные — нет в фидах'!$A$3:$C$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Разбор прайса'!$A$3:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Параметры прогона'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сводка'!$A$3:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Расхождения'!$A$3:$K$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Пропущено — красные строки'!$A$3:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Нет в прайсе'!$A$3:$G$447</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'В прайсе, но не зелёные'!$A$3:$H$625</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Кириллица в артикуле'!$A$3:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Зелёные — нет в фидах'!$A$3:$C$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Красная разметка фидов'!$A$3:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Разбор прайса'!$A$3:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Параметры прогона'!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -88,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -103,6 +107,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -476,16 +481,17 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Обновлялись только цены, подсвеченные в прайсе зелёным. Прочие поля фидов не изменялись.</t>
+          <t>Обновлялись только цены, подсвеченные в прайсе зелёным, и только в строках, НЕ помеченных красным в самом фиде. Прочие поля фидов не изменялись.</t>
         </is>
       </c>
     </row>
@@ -517,20 +523,25 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Пропущено (красная строка)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Зелёная, цена совпадала</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>В прайсе, но не зелёная</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Нет в прайсе</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Без старой цены</t>
         </is>
@@ -556,18 +567,21 @@
         <v>472</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>222</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>201</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>48</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -594,15 +608,18 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>220</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>237</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>314</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -626,18 +643,21 @@
         <v>449</v>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>34</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>184</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>82</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,29 +683,167 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>нет артикулов</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I7"/>
+  <autoFilter ref="A3:J7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Файл прайса</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Прайс GENGLASS 2026 дилерский.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Что обновляли</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>только цены с зелёной заливкой #D9EAD3 в колонке «ЕРЦ»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Что не меняли</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>все остальные поля фидов — без изменений; строки, помеченные красным в фиде, пропущены</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Нормализация артикула</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>trim, схлопывание пробелов (вкл. NBSP), UPPER, срез ведущих нулей</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Многострочные артикулы</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ячейка «Артикул» разбивается по переводу строки; все артикулы строки получают её цену «ЕРЦ»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>не применялось — цена перенесена как в прайсе</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Артикулов с новой ценой</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Всего позиций обновлено</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>М&amp;M</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>В файле нет колонки с артикулом — матчинг по артикулу неприменим. Файл оставлен без изменений (согласовано).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -696,12 +854,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
@@ -887,16 +1045,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-2-180-90</t>
+          <t>GGT-28-1-3-180-90</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-2-180-90</t>
+          <t>GGT-28-1-3-180-90</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
@@ -934,16 +1092,16 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-3-180-90</t>
+          <t>GGT-28-3-3-180-90</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-3-180-90</t>
+          <t>GGT-28-3-3-180-90</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -1028,16 +1186,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-3-180-90</t>
+          <t>GGT-28-2-3-180-90</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-3-180-90</t>
+          <t>GGT-28-2-3-180-90</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -1075,16 +1233,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-1-180-90</t>
+          <t>GGT-28-3-1-180-90</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-1-1-180-90</t>
+          <t>GGT-28-3-1-180-90</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -1122,16 +1280,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-1-180-90</t>
+          <t>GGT-28-3-2-180-90</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-1-180-90</t>
+          <t>GGT-28-3-2-180-90</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -1169,16 +1327,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-2-180-90</t>
+          <t>GGT-28-1-1-180-90</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-3-2-180-90</t>
+          <t>GGT-28-1-1-180-90</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -1216,16 +1374,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-2-2-180-90</t>
+          <t>GGT-28-1-2-180-90</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-2-2-180-90</t>
+          <t>GGT-28-1-2-180-90</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -1263,16 +1421,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-2-3-180-90</t>
+          <t>GGT-28-2-2-180-90</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>GGT-28-2-3-180-90</t>
+          <t>GGT-28-2-2-180-90</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -1498,16 +1656,16 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-120</t>
+          <t>GGK-02-1-3-120</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-120</t>
+          <t>GGK-02-1-3-120</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -1545,16 +1703,16 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-2-120</t>
+          <t>GGK-02-3-2-120</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-2-120</t>
+          <t>GGK-02-3-2-120</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1639,16 +1797,16 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-120</t>
+          <t>GGK-02-2-2-120</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-120</t>
+          <t>GGK-02-2-2-120</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
@@ -1686,16 +1844,16 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-120</t>
+          <t>GGK-02-2-3-120</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-120</t>
+          <t>GGK-02-2-3-120</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
@@ -1827,16 +1985,16 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-3-80</t>
+          <t>GGK-02-3-2-80</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-3-80</t>
+          <t>GGK-02-3-2-80</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -1874,16 +2032,16 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-2-80</t>
+          <t>GGK-02-3-3-80</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-2-80</t>
+          <t>GGK-02-3-3-80</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
@@ -1921,16 +2079,16 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-80</t>
+          <t>GGK-02-1-2-80</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-80</t>
+          <t>GGK-02-1-2-80</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
@@ -1968,16 +2126,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-80</t>
+          <t>GGK-02-1-3-80</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-80</t>
+          <t>GGK-02-1-3-80</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
@@ -2015,16 +2173,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-80</t>
+          <t>GGK-02-2-3-80</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-80</t>
+          <t>GGK-02-2-3-80</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
@@ -2062,16 +2220,16 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-2-1</t>
+          <t>GGM-23-3-1</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-2-1</t>
+          <t>GGM-23-3-1</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
@@ -2109,16 +2267,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-3-1</t>
+          <t>GGM-23-1-1</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-3-1</t>
+          <t>GGM-23-1-1</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
@@ -2156,16 +2314,16 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-1-1</t>
+          <t>GGM-23-2-1</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>GGM-23-1-1</t>
+          <t>GGM-23-2-1</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
@@ -2203,16 +2361,16 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-3-100</t>
+          <t>GGL-06-L-2</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-3-100</t>
+          <t>GGL-06-L-2</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
@@ -2229,7 +2387,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Консолитумбы r4</t>
+          <t>Безрамные зеркала с подсветкой r21</t>
         </is>
       </c>
     </row>
@@ -2250,16 +2408,16 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-2-100</t>
+          <t>GGK-02-1-3-100</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-2-100</t>
+          <t>GGK-02-1-3-100</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
@@ -2297,16 +2455,16 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-100</t>
+          <t>GGK-02-2-2-100</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-3-100</t>
+          <t>GGK-02-2-2-100</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -2344,16 +2502,16 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-2-100</t>
+          <t>GGK-02-2-3-100</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-1-2-100</t>
+          <t>GGK-02-2-3-100</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -2391,16 +2549,16 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>GGL-05-XL-slim-2</t>
+          <t>GGK-02-3-3-100</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>GGL-05-XL-SLIM-2</t>
+          <t>GGK-02-3-3-100</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -2417,7 +2575,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Безрамные зеркала с подсветкой r17</t>
+          <t>Консолитумбы r4</t>
         </is>
       </c>
     </row>
@@ -2438,16 +2596,16 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-100</t>
+          <t>GGL-05-XL-slim-2</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-3-2-100</t>
+          <t>GGL-05-XL-SLIM-2</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
@@ -2464,7 +2622,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Консолитумбы r4</t>
+          <t>Безрамные зеркала с подсветкой r17</t>
         </is>
       </c>
     </row>
@@ -2485,16 +2643,16 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-100</t>
+          <t>GGK-02-1-2-100</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>GGK-02-2-3-100</t>
+          <t>GGK-02-1-2-100</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
@@ -2532,16 +2690,16 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>GGL-06-L-2</t>
+          <t>GGK-02-3-2-100</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>GGL-06-L-2</t>
+          <t>GGK-02-3-2-100</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
@@ -2558,7 +2716,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Безрамные зеркала с подсветкой r21</t>
+          <t>Консолитумбы r4</t>
         </is>
       </c>
     </row>
@@ -2579,16 +2737,16 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-1-1</t>
+          <t>GGM-16-2-1</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-1-1</t>
+          <t>GGM-16-2-1</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
@@ -2626,16 +2784,16 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-2-1</t>
+          <t>GGM-16-1-1</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-2-1</t>
+          <t>GGM-16-1-1</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
@@ -2861,16 +3019,16 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>410</v>
+        <v>55</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-4</t>
+          <t>GGR-10-2</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-4</t>
+          <t>GGR-10-2</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
@@ -2955,16 +3113,16 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>55</v>
+        <v>410</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-2</t>
+          <t>GGR-10-4</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-2</t>
+          <t>GGR-10-4</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
@@ -2988,47 +3146,47 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Genglass / Basicdecor</t>
+          <t>MEBHOME</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Genglass_фиды_Инфографика_Basicdecor_5.08.xls</t>
+          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Выгрузка товаров</t>
+          <t>Лист3</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-4</t>
+          <t>GGT-03-1-2-L-90-12090</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>GGR-10-4</t>
+          <t>GGT-03-1-2-L-90-12090</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>12900</v>
+        <v>39900</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>15900</v>
+        <v>48900</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>0.2325581395348837</v>
+        <v>0.2255639097744361</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Хранение (вешалки) r3</t>
+          <t>Обеденныерабочие столы r18</t>
         </is>
       </c>
     </row>
@@ -3049,16 +3207,16 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-6-L-90-12090</t>
+          <t>GGT-03-2-6-L-90-12090</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-6-L-90-12090</t>
+          <t>GGT-03-2-6-L-90-12090</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
@@ -3096,16 +3254,16 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-90-12090</t>
+          <t>GGT-03-2-3-L-90-12090</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-90-12090</t>
+          <t>GGT-03-2-3-L-90-12090</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
@@ -3143,16 +3301,16 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-90-12090</t>
+          <t>GGT-03-1-6-L-90-12090</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-90-12090</t>
+          <t>GGT-03-1-6-L-90-12090</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
@@ -3190,16 +3348,16 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-6-L-90-12090</t>
+          <t>GGT-03-1-3-L-90-12090</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-6-L-90-12090</t>
+          <t>GGT-03-1-3-L-90-12090</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
@@ -3237,16 +3395,16 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-90-12090</t>
+          <t>GGT-03-3-6-L-90-12090</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-90-12090</t>
+          <t>GGT-03-3-6-L-90-12090</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
@@ -3284,16 +3442,16 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-90-12090</t>
+          <t>GGT-03-3-3-L-90-12090</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-90-12090</t>
+          <t>GGT-03-3-3-L-90-12090</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
@@ -3331,16 +3489,16 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-90-12090</t>
+          <t>GGT-03-3-2-L-90-12090</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-90-12090</t>
+          <t>GGT-03-3-2-L-90-12090</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
@@ -3378,16 +3536,16 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-6-L-90-12090</t>
+          <t>GGT-03-2-2-L-90-12090</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-6-L-90-12090</t>
+          <t>GGT-03-2-2-L-90-12090</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
@@ -3425,33 +3583,33 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>328</v>
+        <v>67</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-90-12090</t>
+          <t>GGL-01-XL-2</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-90-12090</t>
+          <t>GGL-01-XL-2</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>39900</v>
+        <v>27900</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>48900</v>
+        <v>33900</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0.2255639097744361</v>
+        <v>0.2150537634408602</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r18</t>
+          <t>Безрамные зеркала с подсветкой r8</t>
         </is>
       </c>
     </row>
@@ -3472,33 +3630,33 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>GGL-01-XL-2</t>
+          <t>GGM-16-2-2</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>GGL-01-XL-2</t>
+          <t>GGM-16-2-2</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>27900</v>
+        <v>18900</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>33900</v>
+        <v>22900</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.2150537634408602</v>
+        <v>0.2116402116402116</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Безрамные зеркала с подсветкой r8</t>
+          <t>Зеркала в раме r13</t>
         </is>
       </c>
     </row>
@@ -3519,16 +3677,16 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-2-2</t>
+          <t>GGM-16-1-2</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-2-2</t>
+          <t>GGM-16-1-2</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
@@ -3566,33 +3724,33 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-1-2</t>
+          <t>GGR-11-3</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>GGM-16-1-2</t>
+          <t>GGR-11-3</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>18900</v>
+        <v>14900</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>22900</v>
+        <v>17900</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0.2116402116402116</v>
+        <v>0.2013422818791946</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r13</t>
+          <t>Хранение (вешалки) r4</t>
         </is>
       </c>
     </row>
@@ -3613,16 +3771,16 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-2</t>
+          <t>GGR-11-1</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-2</t>
+          <t>GGR-11-1</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
@@ -3660,16 +3818,16 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-3</t>
+          <t>GGR-11-2</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-3</t>
+          <t>GGR-11-2</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
@@ -3707,33 +3865,33 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-1</t>
+          <t>GGM-17-2-3</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>GGR-11-1</t>
+          <t>GGM-17-2-3</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>14900</v>
+        <v>24900</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>17900</v>
+        <v>29900</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0.2013422818791946</v>
+        <v>0.2008032128514056</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Хранение (вешалки) r4</t>
+          <t>Зеркала в раме r19</t>
         </is>
       </c>
     </row>
@@ -3754,16 +3912,16 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-1</t>
+          <t>GGM-17-1-3</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-1</t>
+          <t>GGM-17-1-3</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
@@ -3780,7 +3938,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r7</t>
+          <t>Зеркала в раме r19</t>
         </is>
       </c>
     </row>
@@ -3801,16 +3959,16 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-2-1</t>
+          <t>GGM-15-1-1</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-2-1</t>
+          <t>GGM-15-1-1</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
@@ -3848,16 +4006,16 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>GGM-17-2-3</t>
+          <t>GGM-15-2-1</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>GGM-17-2-3</t>
+          <t>GGM-15-2-1</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
@@ -3874,7 +4032,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r19</t>
+          <t>Зеркала в раме r7</t>
         </is>
       </c>
     </row>
@@ -3942,33 +4100,33 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>GGM-17-1-3</t>
+          <t>GGT-03-2-2-M-80</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>GGM-17-1-3</t>
+          <t>GGT-03-2-2-M-80</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>29900</v>
+        <v>31900</v>
       </c>
       <c r="I71" s="4" t="n">
         <v>5000</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>0.2008032128514056</v>
+        <v>0.1858736059479554</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r19</t>
+          <t>Журнальные столики r4</t>
         </is>
       </c>
     </row>
@@ -3989,16 +4147,16 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-80</t>
+          <t>GGT-03-3-2-M-80</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-80</t>
+          <t>GGT-03-3-2-M-80</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
@@ -4036,16 +4194,16 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-80</t>
+          <t>GGT-03-2-3-M-80</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-80</t>
+          <t>GGT-03-2-3-M-80</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
@@ -4083,16 +4241,16 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-M-80</t>
+          <t>GGT-03-1-3-M-80</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-M-80</t>
+          <t>GGT-03-1-3-M-80</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
@@ -4130,16 +4288,16 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-80</t>
+          <t>GGT-03-1-2-M-80</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-80</t>
+          <t>GGT-03-1-2-M-80</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
@@ -4177,16 +4335,16 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-80</t>
+          <t>GGT-03-3-3-M-80</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-80</t>
+          <t>GGT-03-3-3-M-80</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
@@ -4224,33 +4382,33 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-80</t>
+          <t>GGM-15-1-2</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-80</t>
+          <t>GGM-15-1-2</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>26900</v>
+        <v>27900</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>31900</v>
+        <v>32900</v>
       </c>
       <c r="I77" s="4" t="n">
         <v>5000</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.1858736059479554</v>
+        <v>0.1792114695340502</v>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>Журнальные столики r4</t>
+          <t>Зеркала в раме r11</t>
         </is>
       </c>
     </row>
@@ -4318,33 +4476,33 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2</t>
+          <t>GGT-03-2-3-M-100</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2</t>
+          <t>GGT-03-2-3-M-100</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>27900</v>
+        <v>28900</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>32900</v>
+        <v>33900</v>
       </c>
       <c r="I79" s="4" t="n">
         <v>5000</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>0.1792114695340502</v>
+        <v>0.1730103806228374</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r11</t>
+          <t>Журнальные столики r5</t>
         </is>
       </c>
     </row>
@@ -4412,16 +4570,16 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-100</t>
+          <t>GGT-03-1-3-M-100</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-100</t>
+          <t>GGT-03-1-3-M-100</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
@@ -4459,16 +4617,16 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-100</t>
+          <t>GGT-03-1-2-M-100</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-100</t>
+          <t>GGT-03-1-2-M-100</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
@@ -4506,16 +4664,16 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-100</t>
+          <t>GGT-03-3-2-M-100</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-100</t>
+          <t>GGT-03-3-2-M-100</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
@@ -4553,16 +4711,16 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-100</t>
+          <t>GGT-03-3-3-M-100</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-100</t>
+          <t>GGT-03-3-3-M-100</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
@@ -4600,33 +4758,33 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-100</t>
+          <t>GGT-03-2-3-M-60</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-100</t>
+          <t>GGT-03-2-3-M-60</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
+        <v>24900</v>
+      </c>
+      <c r="H85" s="4" t="n">
         <v>28900</v>
       </c>
-      <c r="H85" s="4" t="n">
-        <v>33900</v>
-      </c>
       <c r="I85" s="4" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0.1730103806228374</v>
+        <v>0.1606425702811245</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>Журнальные столики r5</t>
+          <t>Журнальные столики r3</t>
         </is>
       </c>
     </row>
@@ -4647,16 +4805,16 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-60</t>
+          <t>GGT-03-1-3-M-60</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-M-60</t>
+          <t>GGT-03-1-3-M-60</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
@@ -4694,16 +4852,16 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-M-60</t>
+          <t>GGT-03-1-2-M-60</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-M-60</t>
+          <t>GGT-03-1-2-M-60</t>
         </is>
       </c>
       <c r="G87" s="4" t="n">
@@ -4741,16 +4899,16 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-60</t>
+          <t>GGT-03-2-2-M-60</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-M-60</t>
+          <t>GGT-03-2-2-M-60</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
@@ -4788,16 +4946,16 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-60</t>
+          <t>GGT-03-3-3-M-60</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-M-60</t>
+          <t>GGT-03-3-3-M-60</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
@@ -4835,16 +4993,16 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-60</t>
+          <t>GGT-03-3-2-M-60</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-M-60</t>
+          <t>GGT-03-3-2-M-60</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
@@ -4882,33 +5040,33 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-60</t>
+          <t>GGT-03-2-3-L-80</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-M-60</t>
+          <t>GGT-03-2-3-L-80</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>24900</v>
+        <v>29900</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>28900</v>
+        <v>33900</v>
       </c>
       <c r="I91" s="4" t="n">
         <v>4000</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>0.1606425702811245</v>
+        <v>0.1337792642140468</v>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>Журнальные столики r3</t>
+          <t>Обеденныерабочие столы r3</t>
         </is>
       </c>
     </row>
@@ -4929,16 +5087,16 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-80</t>
+          <t>GGT-03-1-2-L-80</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-80</t>
+          <t>GGT-03-1-2-L-80</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
@@ -4976,16 +5134,16 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-80</t>
+          <t>GGT-03-3-3-L-80</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-80</t>
+          <t>GGT-03-3-3-L-80</t>
         </is>
       </c>
       <c r="G93" s="4" t="n">
@@ -5023,16 +5181,16 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-80</t>
+          <t>GGT-03-2-2-L-80</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-80</t>
+          <t>GGT-03-2-2-L-80</t>
         </is>
       </c>
       <c r="G94" s="4" t="n">
@@ -5070,16 +5228,16 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-80</t>
+          <t>GGT-03-1-3-L-80</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-80</t>
+          <t>GGT-03-1-3-L-80</t>
         </is>
       </c>
       <c r="G95" s="4" t="n">
@@ -5117,16 +5275,16 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-80</t>
+          <t>GGT-03-3-2-L-80</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-80</t>
+          <t>GGT-03-3-2-L-80</t>
         </is>
       </c>
       <c r="G96" s="4" t="n">
@@ -5164,33 +5322,33 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-80</t>
+          <t>GGM-20-1</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-80</t>
+          <t>GGM-20-1</t>
         </is>
       </c>
       <c r="G97" s="4" t="n">
-        <v>29900</v>
+        <v>39900</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>33900</v>
+        <v>44900</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>0.1337792642140468</v>
+        <v>0.12531328320802</v>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r3</t>
+          <t>Зеркала в раме r23</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5369,16 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>GGM-20-1</t>
+          <t>GGM-20-2</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>GGM-20-1</t>
+          <t>GGM-20-2</t>
         </is>
       </c>
       <c r="G98" s="4" t="n">
@@ -5305,33 +5463,33 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>GGM-20-2</t>
+          <t>GGM-15-1-2-L</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>GGM-20-2</t>
+          <t>GGM-15-1-2-L</t>
         </is>
       </c>
       <c r="G100" s="4" t="n">
-        <v>39900</v>
+        <v>24900</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>44900</v>
+        <v>27900</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.12531328320802</v>
+        <v>0.1204819277108434</v>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r23</t>
+          <t>Зеркала в раме r10</t>
         </is>
       </c>
     </row>
@@ -5352,16 +5510,16 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2-L</t>
+          <t>GGM-15-2-2-L</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2-L</t>
+          <t>GGM-15-2-2-L</t>
         </is>
       </c>
       <c r="G101" s="4" t="n">
@@ -5399,33 +5557,33 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-2-2-L</t>
+          <t>GGM-02-1-2</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-2-2-L</t>
+          <t>GGM-02-1-2</t>
         </is>
       </c>
       <c r="G102" s="4" t="n">
-        <v>24900</v>
+        <v>19900</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>27900</v>
+        <v>21900</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.1204819277108434</v>
+        <v>0.1005025125628141</v>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r10</t>
+          <t>Зеркала в раме r5</t>
         </is>
       </c>
     </row>
@@ -5446,127 +5604,127 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>365</v>
+        <v>9</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2-L</t>
+          <t>GGM-02-2-2</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>GGM-15-1-2-L</t>
+          <t>GGM-02-2-2</t>
         </is>
       </c>
       <c r="G103" s="4" t="n">
-        <v>24900</v>
+        <v>19900</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>27900</v>
+        <v>21900</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>0.1204819277108434</v>
+        <v>0.1005025125628141</v>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r10</t>
+          <t>Зеркала в раме r5</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D104" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>GGM-02-1-2</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>GGM-02-1-2</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>19900</v>
-      </c>
-      <c r="H104" s="4" t="n">
-        <v>21900</v>
-      </c>
-      <c r="I104" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>0.1005025125628141</v>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>Зеркала в раме r5</t>
+      <c r="D104" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-1-5-80</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-1-5-80</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>29900</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>26900</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="J104" s="8" t="n">
+        <v>-0.1003344481605351</v>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Обеденныерабочие столы r51</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D105" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>GGM-02-2-2</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>GGM-02-2-2</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v>19900</v>
-      </c>
-      <c r="H105" s="4" t="n">
-        <v>21900</v>
-      </c>
-      <c r="I105" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>0.1005025125628141</v>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>Зеркала в раме r5</t>
+      <c r="D105" s="6" t="n">
+        <v>441</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-3-5-80</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-3-5-80</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>29900</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>26900</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="J105" s="8" t="n">
+        <v>-0.1003344481605351</v>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>Обеденныерабочие столы r51</t>
         </is>
       </c>
     </row>
@@ -5587,16 +5745,16 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-5-80</t>
+          <t>GGT-47-2-3-80</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-5-80</t>
+          <t>GGT-47-2-3-80</t>
         </is>
       </c>
       <c r="G106" s="7" t="n">
@@ -5634,16 +5792,16 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-2-80</t>
+          <t>GGT-47-1-3-80</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-2-80</t>
+          <t>GGT-47-1-3-80</t>
         </is>
       </c>
       <c r="G107" s="7" t="n">
@@ -5681,16 +5839,16 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-3-80</t>
+          <t>GGT-47-2-5-80</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-3-80</t>
+          <t>GGT-47-2-5-80</t>
         </is>
       </c>
       <c r="G108" s="7" t="n">
@@ -5728,16 +5886,16 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-3-80</t>
+          <t>GGT-47-2-2-80</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-3-80</t>
+          <t>GGT-47-2-2-80</t>
         </is>
       </c>
       <c r="G109" s="7" t="n">
@@ -5759,190 +5917,190 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>GGM-24-1</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>GGM-24-1</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>29900</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>32900</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>0.1003344481605351</v>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>Зеркала в раме r26</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Лист3</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>GGM-24-2</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>GGM-24-2</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>29900</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>32900</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>0.1003344481605351</v>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>Зеркала в раме r26</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Лист3</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="n">
         <v>433</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>GGT-47-1-2-80</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>GGT-47-1-2-80</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G112" s="7" t="n">
         <v>29900</v>
       </c>
-      <c r="H110" s="7" t="n">
+      <c r="H112" s="7" t="n">
         <v>26900</v>
       </c>
-      <c r="I110" s="7" t="n">
+      <c r="I112" s="7" t="n">
         <v>-3000</v>
       </c>
-      <c r="J110" s="8" t="n">
+      <c r="J112" s="8" t="n">
         <v>-0.1003344481605351</v>
       </c>
-      <c r="K110" s="6" t="inlineStr">
+      <c r="K112" s="6" t="inlineStr">
         <is>
           <t>Обеденныерабочие столы r51</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
-        <v>438</v>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-2-5-80</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-2-5-80</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="n">
+      <c r="D113" s="6" t="n">
+        <v>439</v>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-3-2-80</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>GGT-47-3-2-80</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n">
         <v>29900</v>
       </c>
-      <c r="H111" s="7" t="n">
+      <c r="H113" s="7" t="n">
         <v>26900</v>
       </c>
-      <c r="I111" s="7" t="n">
+      <c r="I113" s="7" t="n">
         <v>-3000</v>
       </c>
-      <c r="J111" s="8" t="n">
+      <c r="J113" s="8" t="n">
         <v>-0.1003344481605351</v>
       </c>
-      <c r="K111" s="6" t="inlineStr">
+      <c r="K113" s="6" t="inlineStr">
         <is>
           <t>Обеденныерабочие столы r51</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>MEBHOME</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>Лист3</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>GGM-24-2</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>GGM-24-2</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>29900</v>
-      </c>
-      <c r="H112" s="4" t="n">
-        <v>32900</v>
-      </c>
-      <c r="I112" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J112" s="5" t="n">
-        <v>0.1003344481605351</v>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>Зеркала в раме r26</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>MEBHOME</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>Лист3</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>GGM-24-1</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>GGM-24-1</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="n">
-        <v>29900</v>
-      </c>
-      <c r="H113" s="4" t="n">
-        <v>32900</v>
-      </c>
-      <c r="I113" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0.1003344481605351</v>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>Зеркала в раме r26</t>
         </is>
       </c>
     </row>
@@ -6010,33 +6168,33 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-5-80</t>
+          <t>GGT-47-3-2-90</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-5-80</t>
+          <t>GGT-47-3-2-90</t>
         </is>
       </c>
       <c r="G115" s="7" t="n">
-        <v>29900</v>
+        <v>31900</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>26900</v>
+        <v>28900</v>
       </c>
       <c r="I115" s="7" t="n">
         <v>-3000</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>-0.1003344481605351</v>
+        <v>-0.09404388714733543</v>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r51</t>
+          <t>Обеденныерабочие столы r52</t>
         </is>
       </c>
     </row>
@@ -6057,33 +6215,33 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-2-80</t>
+          <t>GGT-47-3-5-90</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-2-80</t>
+          <t>GGT-47-3-5-90</t>
         </is>
       </c>
       <c r="G116" s="7" t="n">
-        <v>29900</v>
+        <v>31900</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>26900</v>
+        <v>28900</v>
       </c>
       <c r="I116" s="7" t="n">
         <v>-3000</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>-0.1003344481605351</v>
+        <v>-0.09404388714733543</v>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r51</t>
+          <t>Обеденныерабочие столы r52</t>
         </is>
       </c>
     </row>
@@ -6104,16 +6262,16 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-5-90</t>
+          <t>GGT-47-2-3-90</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-5-90</t>
+          <t>GGT-47-2-3-90</t>
         </is>
       </c>
       <c r="G117" s="7" t="n">
@@ -6151,16 +6309,16 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-3-90</t>
+          <t>GGT-47-3-3-90</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-3-90</t>
+          <t>GGT-47-3-3-90</t>
         </is>
       </c>
       <c r="G118" s="7" t="n">
@@ -6245,16 +6403,16 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-3-90</t>
+          <t>GGT-47-1-3-90</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-3-90</t>
+          <t>GGT-47-1-3-90</t>
         </is>
       </c>
       <c r="G120" s="7" t="n">
@@ -6292,16 +6450,16 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-2-90</t>
+          <t>GGT-47-1-5-90</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-3-2-90</t>
+          <t>GGT-47-1-5-90</t>
         </is>
       </c>
       <c r="G121" s="7" t="n">
@@ -6339,16 +6497,16 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-3-90</t>
+          <t>GGT-47-2-2-90</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-2-3-90</t>
+          <t>GGT-47-2-2-90</t>
         </is>
       </c>
       <c r="G122" s="7" t="n">
@@ -6386,16 +6544,16 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-5-90</t>
+          <t>GGT-47-1-2-90</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>GGT-47-1-5-90</t>
+          <t>GGT-47-1-2-90</t>
         </is>
       </c>
       <c r="G123" s="7" t="n">
@@ -6417,96 +6575,96 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D124" s="6" t="n">
-        <v>445</v>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-2-2-90</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-2-2-90</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="n">
-        <v>31900</v>
-      </c>
-      <c r="H124" s="7" t="n">
-        <v>28900</v>
-      </c>
-      <c r="I124" s="7" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="J124" s="8" t="n">
-        <v>-0.09404388714733543</v>
-      </c>
-      <c r="K124" s="6" t="inlineStr">
-        <is>
-          <t>Обеденныерабочие столы r52</t>
+      <c r="D124" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>GGM-18-2-1</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>GGM-18-2-1</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>21900</v>
+      </c>
+      <c r="H124" s="4" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I124" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>0.091324200913242</v>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>Зеркала в раме r20</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>MEBHOME</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>Лист3</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
-        <v>442</v>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-1-2-90</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>GGT-47-1-2-90</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="n">
-        <v>31900</v>
-      </c>
-      <c r="H125" s="7" t="n">
-        <v>28900</v>
-      </c>
-      <c r="I125" s="7" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="J125" s="8" t="n">
-        <v>-0.09404388714733543</v>
-      </c>
-      <c r="K125" s="6" t="inlineStr">
-        <is>
-          <t>Обеденныерабочие столы r52</t>
+      <c r="D125" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>GGM-18-1-1</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>GGM-18-1-1</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>21900</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I125" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>0.091324200913242</v>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Зеркала в раме r20</t>
         </is>
       </c>
     </row>
@@ -6527,33 +6685,33 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-1-1</t>
+          <t>GGT-03-2-2-L-90</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-1-1</t>
+          <t>GGT-03-2-2-L-90</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>21900</v>
+        <v>32900</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>23900</v>
+        <v>35900</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.091324200913242</v>
+        <v>0.0911854103343465</v>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r20</t>
+          <t>Обеденныерабочие столы r4</t>
         </is>
       </c>
     </row>
@@ -6574,33 +6732,33 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-2-1</t>
+          <t>GGT-03-3-3-L-90</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-2-1</t>
+          <t>GGT-03-3-3-L-90</t>
         </is>
       </c>
       <c r="G127" s="4" t="n">
-        <v>21900</v>
+        <v>32900</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>23900</v>
+        <v>35900</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.091324200913242</v>
+        <v>0.0911854103343465</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r20</t>
+          <t>Обеденныерабочие столы r4</t>
         </is>
       </c>
     </row>
@@ -6621,16 +6779,16 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-90</t>
+          <t>GGT-03-2-3-L-90</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-90</t>
+          <t>GGT-03-2-3-L-90</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
@@ -6715,16 +6873,16 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-90</t>
+          <t>GGT-03-1-2-L-90</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-90</t>
+          <t>GGT-03-1-2-L-90</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
@@ -6762,33 +6920,33 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-90</t>
+          <t>GGM-24-1-M</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-90</t>
+          <t>GGM-24-1-M</t>
         </is>
       </c>
       <c r="G131" s="4" t="n">
-        <v>32900</v>
+        <v>22900</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>35900</v>
+        <v>24900</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>0.0911854103343465</v>
+        <v>0.08733624454148471</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r4</t>
+          <t>Зеркала в раме r25</t>
         </is>
       </c>
     </row>
@@ -6809,33 +6967,33 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-90</t>
+          <t>GGM-24-2-M</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-90</t>
+          <t>GGM-24-2-M</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>32900</v>
+        <v>22900</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>35900</v>
+        <v>24900</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.0911854103343465</v>
+        <v>0.08733624454148471</v>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r4</t>
+          <t>Зеркала в раме r25</t>
         </is>
       </c>
     </row>
@@ -6856,33 +7014,33 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>248</v>
+        <v>383</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>GGM-24-2-M</t>
+          <t>GGT-03-2-5-L-100</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>GGM-24-2-M</t>
+          <t>GGT-03-2-5-L-100</t>
         </is>
       </c>
       <c r="G133" s="4" t="n">
-        <v>22900</v>
+        <v>34900</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>24900</v>
+        <v>37900</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0.08733624454148471</v>
+        <v>0.08595988538681948</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r25</t>
+          <t>Обеденныерабочие столы r5</t>
         </is>
       </c>
     </row>
@@ -6903,33 +7061,33 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>247</v>
+        <v>382</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>GGM-24-1-M</t>
+          <t>GGT-03-1-5-L-100</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>GGM-24-1-M</t>
+          <t>GGT-03-1-5-L-100</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>22900</v>
+        <v>34900</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>24900</v>
+        <v>37900</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.08733624454148471</v>
+        <v>0.08595988538681948</v>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r25</t>
+          <t>Обеденныерабочие столы r5</t>
         </is>
       </c>
     </row>
@@ -6950,16 +7108,16 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>382</v>
+        <v>166</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-5-L-100</t>
+          <t>GGT-03-2-3-L-100</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-5-L-100</t>
+          <t>GGT-03-2-3-L-100</t>
         </is>
       </c>
       <c r="G135" s="4" t="n">
@@ -6997,16 +7155,16 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-100</t>
+          <t>GGT-03-2-2-L-100</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-100</t>
+          <t>GGT-03-2-2-L-100</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
@@ -7044,16 +7202,16 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>163</v>
+        <v>384</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-100</t>
+          <t>GGT-03-3-5-L-100</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-2-L-100</t>
+          <t>GGT-03-3-5-L-100</t>
         </is>
       </c>
       <c r="G137" s="4" t="n">
@@ -7091,16 +7249,16 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>383</v>
+        <v>163</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-5-L-100</t>
+          <t>GGT-03-1-2-L-100</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-5-L-100</t>
+          <t>GGT-03-1-2-L-100</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
@@ -7138,16 +7296,16 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>384</v>
+        <v>164</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-5-L-100</t>
+          <t>GGT-03-1-3-L-100</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-5-L-100</t>
+          <t>GGT-03-1-3-L-100</t>
         </is>
       </c>
       <c r="G139" s="4" t="n">
@@ -7185,16 +7343,16 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-100</t>
+          <t>GGT-03-3-2-L-100</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-100</t>
+          <t>GGT-03-3-2-L-100</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
@@ -7232,16 +7390,16 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-100</t>
+          <t>GGT-03-3-3-L-100</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-100</t>
+          <t>GGT-03-3-3-L-100</t>
         </is>
       </c>
       <c r="G141" s="4" t="n">
@@ -7279,33 +7437,33 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-100</t>
+          <t>GGM-18-2-2</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-3-L-100</t>
+          <t>GGM-18-2-2</t>
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>34900</v>
+        <v>25900</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>37900</v>
+        <v>27900</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>0.08595988538681948</v>
+        <v>0.07722007722007722</v>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r5</t>
+          <t>Зеркала в раме r22</t>
         </is>
       </c>
     </row>
@@ -7326,33 +7484,33 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-100</t>
+          <t>GGM-18-1-2</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-100</t>
+          <t>GGM-18-1-2</t>
         </is>
       </c>
       <c r="G143" s="4" t="n">
-        <v>34900</v>
+        <v>25900</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>37900</v>
+        <v>27900</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>0.08595988538681948</v>
+        <v>0.07722007722007722</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>Обеденныерабочие столы r5</t>
+          <t>Зеркала в раме r22</t>
         </is>
       </c>
     </row>
@@ -7373,16 +7531,16 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-1-2</t>
+          <t>GGM-18-3-2</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-1-2</t>
+          <t>GGM-18-3-2</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
@@ -7420,33 +7578,33 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-2-2</t>
+          <t>GGL-07-XL-2</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-2-2</t>
+          <t>GGL-07-XL-2</t>
         </is>
       </c>
       <c r="G145" s="4" t="n">
-        <v>25900</v>
+        <v>29900</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="I145" s="4" t="n">
         <v>2000</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>0.07722007722007722</v>
+        <v>0.06688963210702341</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r22</t>
+          <t>Безрамные зеркала с подсветкой r23</t>
         </is>
       </c>
     </row>
@@ -7467,33 +7625,33 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-3-2</t>
+          <t>GGT-03-3-2-L-110</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>GGM-18-3-2</t>
+          <t>GGT-03-3-2-L-110</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>25900</v>
+        <v>37900</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>27900</v>
+        <v>38900</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>0.07722007722007722</v>
+        <v>0.02638522427440633</v>
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>Зеркала в раме r22</t>
+          <t>Обеденныерабочие столы r7</t>
         </is>
       </c>
     </row>
@@ -7514,33 +7672,33 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>GGL-07-XL-2</t>
+          <t>GGT-03-3-3-L-110</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>GGL-07-XL-2</t>
+          <t>GGT-03-3-3-L-110</t>
         </is>
       </c>
       <c r="G147" s="4" t="n">
-        <v>29900</v>
+        <v>37900</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>31900</v>
+        <v>38900</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>0.06688963210702341</v>
+        <v>0.02638522427440633</v>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>Безрамные зеркала с подсветкой r23</t>
+          <t>Обеденныерабочие столы r7</t>
         </is>
       </c>
     </row>
@@ -7561,16 +7719,16 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-110</t>
+          <t>GGT-03-1-2-L-110</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-3-L-110</t>
+          <t>GGT-03-1-2-L-110</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
@@ -7608,16 +7766,16 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-110</t>
+          <t>GGT-03-1-3-L-110</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-2-2-L-110</t>
+          <t>GGT-03-1-3-L-110</t>
         </is>
       </c>
       <c r="G149" s="4" t="n">
@@ -7655,16 +7813,16 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-110</t>
+          <t>GGT-03-2-2-L-110</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-1-3-L-110</t>
+          <t>GGT-03-2-2-L-110</t>
         </is>
       </c>
       <c r="G150" s="4" t="n">
@@ -7702,16 +7860,16 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-110</t>
+          <t>GGT-03-2-3-L-110</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>GGT-03-3-2-L-110</t>
+          <t>GGT-03-2-3-L-110</t>
         </is>
       </c>
       <c r="G151" s="4" t="n">
@@ -7732,107 +7890,199 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>MEBHOME</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>Лист3</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>GGT-03-2-3-L-110</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>GGT-03-2-3-L-110</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="n">
-        <v>37900</v>
-      </c>
-      <c r="H152" s="4" t="n">
-        <v>38900</v>
-      </c>
-      <c r="I152" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>0.02638522427440633</v>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>Обеденныерабочие столы r7</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>MEBHOME</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>Лист3</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>GGT-03-1-2-L-110</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>GGT-03-1-2-L-110</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="n">
-        <v>37900</v>
-      </c>
-      <c r="H153" s="4" t="n">
-        <v>38900</v>
-      </c>
-      <c r="I153" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J153" s="5" t="n">
-        <v>0.02638522427440633</v>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>Обеденныерабочие столы r7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:K153"/>
+  <autoFilter ref="A3:K151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>В прайсе цена подсвечена зелёным, но строка помечена красным в самом фиде — по договорённости не меняли. Колонка «Новая цена» показывает, что было бы применено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Партнёр</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Файл</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Артикул (исходный)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Артикул (норм.)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Старая цена</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Новая цена</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Дельта</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Дельта %</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Источник в прайсе</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Genglass / Basicdecor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Genglass_фиды_Инфографика_Basicdecor_5.08.xls</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Выгрузка товаров</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>423</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GGR-10-4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GGR-10-4</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>12900</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>15900</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Хранение (вешалки) r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Лист3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>365</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GGM-15-1-2-L</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GGM-15-1-2-L</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>24900</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>27900</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0.1204819277108434</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Зеркала в раме r10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22552,7 +22802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45018,7 +45268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45740,7 +45990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46144,7 +46394,257 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Заливки строк, распознанные как «красные» (тон HSV ≤20° или ≥320°, насыщенность ≥0,05). Оранжевые, жёлтые, зелёные и серые пометки красными не считаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Партнёр</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Заливка строки</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Строк</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Считается красной</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Genglass / Basicdecor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Genglass / Basicdecor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>#FF99CC</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>106</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Genglass / Basicdecor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#FFFFCC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>InMyRoom</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>473</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>InMyRoom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>#FF8080</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>404</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>InMyRoom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>#CCFFCC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>тема/без заливки</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>315</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>#FFFFFF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>126</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>#D99594</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>84</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEBHOME</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>#F4CCCC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46456,139 +46956,4 @@
   <autoFilter ref="A3:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Файл прайса</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Прайс GENGLASS 2026 дилерский.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Что обновляли</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>только цены с зелёной заливкой #D9EAD3 в колонке «ЕРЦ»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Что не меняли</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>все остальные поля фидов — без изменений</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Нормализация артикула</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>trim, схлопывание пробелов (вкл. NBSP), UPPER, срез ведущих нулей</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Многострочные артикулы</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ячейка «Артикул» разбивается по переводу строки; все артикулы строки получают её цену «ЕРЦ»</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Округление</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>не применялось — цена перенесена как в прайсе</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Артикулов с новой ценой</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Всего позиций обновлено</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>М&amp;M</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>В файле нет колонки с артикулом — матчинг по артикулу неприменим. Файл оставлен без изменений (согласовано).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>